--- a/output/14_Aviat_Ceragon_기능별_비교.xlsx
+++ b/output/14_Aviat_Ceragon_기능별_비교.xlsx
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>393069.6</v>
+        <v>377188</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>749034</v>
+        <v>718768</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1577,11 +1577,11 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="n">
-        <v>35356545.59</v>
+        <v>35340663.99</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>47432792.34</v>
+        <v>47402526.34</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>578476.8</v>
+        <v>555104</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1290405.6</v>
+        <v>1238264</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -2139,11 +2139,11 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="n">
-        <v>55426376.53999999</v>
+        <v>55403003.73999999</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>65593357.738</v>
+        <v>65541216.138</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>393069.6</v>
+        <v>377188</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>749034</v>
+        <v>718768</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -2735,11 +2735,11 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="n">
-        <v>35356545.59</v>
+        <v>35340663.99</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>47431698.104</v>
+        <v>47401432.104</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>578476.8</v>
+        <v>555104</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1290405.6</v>
+        <v>1238264</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -3297,11 +3297,11 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="n">
-        <v>55424188.068</v>
+        <v>55400815.268</v>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>65591169.266</v>
+        <v>65539027.66599999</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -3443,16 +3443,16 @@
         <v>32808288</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>35356545.59</v>
+        <v>35340663.99</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>47432792.34</v>
+        <v>47402526.34</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>47710885.87800001</v>
+        <v>47680619.87800001</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
         <v>47007556</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>55426376.53999999</v>
+        <v>55403003.73999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>65593357.738</v>
+        <v>65541216.138</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>55704470.07799999</v>
+        <v>55681097.278</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>65924718.84</v>
+        <v>65872577.23999999</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -3521,16 +3521,16 @@
         <v>26625786</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>35356545.59</v>
+        <v>35340663.99</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>47431698.104</v>
+        <v>47401432.104</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>47709791.642</v>
+        <v>47679525.642</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -3559,16 +3559,16 @@
         <v>40129488</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>55424188.068</v>
+        <v>55400815.268</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>65591169.266</v>
+        <v>65539027.66599999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>55702281.606</v>
+        <v>55678908.806</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>65922530.36799999</v>
+        <v>65870388.76799999</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
